--- a/backend/data/financials_by_company/1QJ.F.xlsx
+++ b/backend/data/financials_by_company/1QJ.F.xlsx
@@ -4107,10 +4107,8 @@
           <t>Stans</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>6370</t>
-        </is>
+      <c r="C2" t="n">
+        <v>6370</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -4240,7 +4238,7 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>Infinity</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AM2" t="n">
